--- a/data/trans_orig/IP13_R1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R1_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96440</t>
+          <t>95714</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103139</t>
+          <t>103113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130055</t>
+          <t>130040</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229116</t>
+          <t>228828</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238363</t>
+          <t>238251</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90872</t>
+          <t>91123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88542</t>
+          <t>88832</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182756</t>
+          <t>182200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>189286</t>
+          <t>189574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47891</t>
+          <t>48095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60922</t>
+          <t>60638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>111392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115325</t>
+          <t>115314</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>210485</t>
+          <t>210853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217308</t>
+          <t>217442</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>208906</t>
+          <t>207906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>216556</t>
+          <t>216621</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>422977</t>
+          <t>423443</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>432843</t>
+          <t>433217</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115163</t>
+          <t>114664</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155551</t>
+          <t>156026</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162087</t>
+          <t>161864</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273008</t>
+          <t>272802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64255</t>
+          <t>64818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136444</t>
+          <t>136083</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15195</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31415</t>
+          <t>31699</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>640323</t>
+          <t>640684</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>651208</t>
+          <t>651574</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>728814</t>
+          <t>729455</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>741399</t>
+          <t>741622</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1374424</t>
+          <t>1374140</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1390644</t>
+          <t>1389975</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_R1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R1_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6419</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3773</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8748</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>120212</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>115619</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>122038</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>100689</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>95714</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>103113</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>134477</t>
+          <t>99070</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130040</t>
+          <t>93927</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>101552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>235167</t>
+          <t>219282</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228828</t>
+          <t>213742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238251</t>
+          <t>222694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122038</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122038</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122038</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>240646</t>
+          <t>224965</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240646</t>
+          <t>224965</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240646</t>
+          <t>224965</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2422</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6832</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3558</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6741</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88976</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84566</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>90931</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>94030</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>91123</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>95904</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>93206</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>96546</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>93044</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>88832</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>95025</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,95%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>268</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>187073</t>
+          <t>184879</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182200</t>
+          <t>180033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>189574</t>
+          <t>187023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2432</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3766</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3681</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3215</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56486</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54509</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>50801</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>48095</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>52494</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>49801</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>53482</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>93,12%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>63304</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>60638</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>63853</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,97%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>156</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>114105</t>
+          <t>108980</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111392</t>
+          <t>106216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115314</t>
+          <t>110087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4025</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2753</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7157</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>197919</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>191999</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>200509</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>215257</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>210853</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>217442</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>213903</t>
+          <t>175949</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207906</t>
+          <t>171429</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>216621</t>
+          <t>177860</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>429160</t>
+          <t>373869</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>423443</t>
+          <t>367803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433217</t>
+          <t>377467</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7338</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4764</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>339</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>145573</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>140905</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147515</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>117901</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>114664</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>119040</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>159907</t>
+          <t>117234</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156026</t>
+          <t>114219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161864</t>
+          <t>118392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>277809</t>
+          <t>262808</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272802</t>
+          <t>258077</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>280218</t>
+          <t>265258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,107 +2435,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4077</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3681</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4240</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4815</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2548,74 +2548,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>68080</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>64818</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>69666</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>66675</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>70356</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>94,77%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72003</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>188</t>
@@ -2623,27 +2623,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>140083</t>
+          <t>137954</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136083</t>
+          <t>134404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15864</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>677453</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>670004</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>682644</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>913</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>646758</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>640684</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>651574</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>736638</t>
+          <t>610319</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>729455</t>
+          <t>602949</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>741622</t>
+          <t>614523</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1383396</t>
+          <t>1287771</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1374140</t>
+          <t>1279267</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1389975</t>
+          <t>1294766</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>688851</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>688851</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>688851</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>748502</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>748502</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>748502</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1405839</t>
+          <t>1309707</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1405839</t>
+          <t>1309707</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1405839</t>
+          <t>1309707</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
